--- a/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
+++ b/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd82f5644ba374c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rab0964cf40e64da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="Rbfedeee1378849ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="R0919ce0b30ec468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="Rd5017f6ffca8458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="R8a3f5605e86e40ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R9d1918a9e1324ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R23dd138fa70348b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="Ra4fb9c08fb294640"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="Rfc3bbe5759ca4588"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Rc0465d89686a4ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Rc9a3c10607ae43ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="Ra37e3b54cea040ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="R78e1fc0d26c14ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="R6ab3115d39e44620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="R3b3aa187c07a456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="Ra99190a8e71e4127"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="R6e832ca65e7a4a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="R311865ce5f854b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="R7e3e50c9b3c746a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="Reac2835888944091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Reb1ef3c5b470490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rf1474cbdf2404cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="R6092b5797a6b4979"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="Rad83157399e74ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="R288b8a464b794c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="Rbeaabef433184795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R3c0bf647f1b7471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R23a77d67f4d34f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="R7e97ffa0467645b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="R95a3edbe7ec944d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Rb5413181fcc74c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Ra7696a7a9aba4612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="R6a3539d791484b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="Re9ffa92a332d4129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="Rbcac1f96f1e444f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="Rb3018fadd32948f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="Rddd04c6c67024c41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="Rcbcaf67add2d46b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="R0147ab05e3b343ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="Re15ca0273c674c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="R150aea620ddd48f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,11 +33,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="hh:mm"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="204" formatCode="h:mm"/>
+    <x:numFmt numFmtId="205" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -79,7 +81,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -119,6 +121,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFAFAFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -176,7 +203,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -281,6 +308,34 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -34068,156 +34123,144 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="25" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="57" t="str">
         <x:v>key</x:v>
       </x:c>
-      <x:c r="B1" s="26" t="str">
+      <x:c r="B1" s="58" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="C1" s="27" t="str">
+      <x:c r="C1" s="59" t="str">
         <x:v>comment</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="6" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="61" t="str">
         <x:v>Language</x:v>
       </x:c>
-      <x:c r="B2" s="29" t="str">
+      <x:c r="B2" s="68" t="str">
         <x:v>ru</x:v>
       </x:c>
-      <x:c r="C2" s="35" t="str">
+      <x:c r="C2" s="67" t="str">
         <x:v>Язык интерфейса: uk, ru или en.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="6" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="61" t="str">
         <x:v>TimeZone</x:v>
       </x:c>
-      <x:c r="B3" s="29" t="str">
+      <x:c r="B3" s="68" t="str">
         <x:v>Europe/Kyiv</x:v>
       </x:c>
-      <x:c r="C3" s="35" t="str">
+      <x:c r="C3" s="67" t="str">
         <x:v>Часовой пояс Apps Script, таблицы и календарей должен совпадать.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="6" t="str">
-        <x:v>ClientBotToken</x:v>
-      </x:c>
-      <x:c r="B4" s="33" t="str">
-        <x:v>PASTE_CLIENT_BOT_TOKEN</x:v>
-      </x:c>
-      <x:c r="C4" s="35" t="str">
-        <x:v>Токен Client Bot из @BotFather. Обязательная замена.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="6" t="str">
-        <x:v>AdminBotToken</x:v>
-      </x:c>
-      <x:c r="B5" s="33" t="str">
-        <x:v>PASTE_ADMIN_BOT_TOKEN</x:v>
-      </x:c>
-      <x:c r="C5" s="35" t="str">
-        <x:v>Токен Admin Bot из @BotFather. Обязательная замена.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="6" t="str">
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="61" t="str">
         <x:v>AppsScriptUrl</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>PASTE_WEB_APP_EXEC_URL</x:v>
-      </x:c>
-      <x:c r="C6" s="35" t="str">
+      <x:c r="B4" s="69" t="str">
+        <x:v>PASTE_APPS_SCRIPT_EXEC_URL</x:v>
+      </x:c>
+      <x:c r="C4" s="67" t="str">
         <x:v>URL production Web App, оканчивающийся на /exec. Обязательная замена после deployment.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="6" t="str">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="61" t="str">
         <x:v>AdminTelegramIds</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="str">
-        <x:v>PASTE_FIRST_ADMIN_TELEGRAM_ID</x:v>
-      </x:c>
-      <x:c r="C7" s="35" t="str">
+      <x:c r="B5" s="69" t="str">
+        <x:v>PASTE_ADMIN_TELEGRAM_ID</x:v>
+      </x:c>
+      <x:c r="C5" s="67" t="str">
         <x:v>Telegram ID первого администратора. Несколько ID — через запятую. Хранить как текст.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="6" t="str">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="61" t="str">
         <x:v>ReminderDayBefore</x:v>
       </x:c>
-      <x:c r="B8" s="30" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="35" t="str">
+      <x:c r="B6" s="62" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C6" s="67" t="str">
         <x:v>Включить напоминание клиенту за день до записи.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="6" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="61" t="str">
         <x:v>DefaultCalendarId</x:v>
       </x:c>
-      <x:c r="B9" s="29" t="str">
+      <x:c r="B7" s="68" t="str">
         <x:v>primary</x:v>
       </x:c>
-      <x:c r="C9" s="35" t="str">
+      <x:c r="C7" s="67" t="str">
         <x:v>Резервный Calendar ID. Для мастеров предпочтительны отдельные calendar_id.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="6" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="61" t="str">
         <x:v>DefaultWorkStartTime</x:v>
       </x:c>
-      <x:c r="B10" s="36" t="n">
+      <x:c r="B8" s="70" t="n">
         <x:v>0.375</x:v>
       </x:c>
-      <x:c r="C10" s="35" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>Начало графика по умолчанию для нового мастера.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="6" t="str">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="61" t="str">
         <x:v>DefaultWorkEndTime</x:v>
       </x:c>
-      <x:c r="B11" s="36" t="n">
+      <x:c r="B9" s="70" t="n">
         <x:v>0.8333333333333334</x:v>
       </x:c>
-      <x:c r="C11" s="35" t="str">
+      <x:c r="C9" s="67" t="str">
         <x:v>Конец графика по умолчанию для нового мастера.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="61" t="str">
+        <x:v>BookingDaysAhead</x:v>
+      </x:c>
+      <x:c r="B10" s="71" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C10" s="67" t="str">
+        <x:v>Горизонт записи: целое число от 1 до 365.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="61" t="str">
+        <x:v>PaginationPageSize</x:v>
+      </x:c>
+      <x:c r="B11" s="71" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="67" t="str">
+        <x:v>Количество элементов на странице: целое число от 1 до 10.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12">
-      <x:c r="A12" s="6" t="str">
-        <x:v>BookingDaysAhead</x:v>
-      </x:c>
-      <x:c r="B12" s="29" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="35" t="str">
-        <x:v>Горизонт записи: целое число от 1 до 365.</x:v>
-      </x:c>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="6" t="str">
-        <x:v>PaginationPageSize</x:v>
-      </x:c>
-      <x:c r="B13" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="35" t="str">
-        <x:v>Количество элементов на странице: целое число от 1 до 10.</x:v>
-      </x:c>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="7">
     <x:dataValidation type="list" sqref="B2">
       <x:formula1>"uk,ru,en"</x:formula1>
     </x:dataValidation>
@@ -34229,6 +34272,17 @@
       <x:formula2>365</x:formula2>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="between" sqref="B13">
+      <x:formula1>1</x:formula1>
+      <x:formula2>10</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B6">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B10">
+      <x:formula1>1</x:formula1>
+      <x:formula2>365</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B11">
       <x:formula1>1</x:formula1>
       <x:formula2>10</x:formula2>
     </x:dataValidation>

--- a/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
+++ b/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Reb1ef3c5b470490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rf1474cbdf2404cea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="R6092b5797a6b4979"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="Rad83157399e74ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="R288b8a464b794c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="Rbeaabef433184795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R3c0bf647f1b7471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R23a77d67f4d34f5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="R7e97ffa0467645b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="R95a3edbe7ec944d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Rb5413181fcc74c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Ra7696a7a9aba4612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="R6a3539d791484b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="Re9ffa92a332d4129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="Rbcac1f96f1e444f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="Rb3018fadd32948f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="Rddd04c6c67024c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="Rcbcaf67add2d46b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="R0147ab05e3b343ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="Re15ca0273c674c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="R150aea620ddd48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2b4eb691fb2a426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Re2192451468c4880"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="Rbe2379dd4dc74719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="Re392f8c210f64b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="R34b455f98eca4eb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="R9dbf2ce8ff1d4b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R0dc4c723d1e74d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R62bec1e69f83461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="R8ddd8a3ef1e14580"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="R274a99bb28cc4c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Ree492371e21c4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Rb6880e787249430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="Rad9eb83faa5542e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="Ra371c632e76c4e83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="R4df2d5b3708e41a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="Rac93220ca00a4a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="R8e3e9088ea7c4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="Rf2be7eaf67b14ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="Ra13bbf7e98844260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="Ra481e153e37946bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="Rc1cb36b4258042ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48010,6 +48010,34 @@
         <x:v>Page size updated</x:v>
       </x:c>
     </x:row>
+    <x:row r="331">
+      <x:c r="A331" t="str">
+        <x:v>REQUEST_CALENDAR_ERROR</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>Не вдалося створити подію в календарі. Перевірте доступ до календаря майстра та повторіть підтвердження заявки.</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>Не удалось создать событие в календаре. Проверьте доступ к календарю мастера и повторите подтверждение заявки.</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>Could not create the Calendar event. Check access to the provider calendar and confirm the request again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" t="str">
+        <x:v>APPOINTMENT_CALENDAR_ERROR</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>Не вдалося оновити запис у календарі. Час запису не змінено. Спробуйте ще раз пізніше або зв’яжіться із салоном.</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>Не удалось обновить запись в календаре. Время записи не изменено. Попробуйте ещё раз позже или свяжитесь с салоном.</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>Could not update the appointment in Calendar. The appointment time was not changed. Try again later or contact the salon.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
+++ b/outputs/smartflow-client-template/SmartFlow Beauty Client Template.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2b4eb691fb2a426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Re2192451468c4880"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="Rbe2379dd4dc74719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="Re392f8c210f64b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="R34b455f98eca4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="R9dbf2ce8ff1d4b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R0dc4c723d1e74d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R62bec1e69f83461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="R8ddd8a3ef1e14580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="R274a99bb28cc4c85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Ree492371e21c4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Rb6880e787249430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="Rad9eb83faa5542e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="Ra371c632e76c4e83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="R4df2d5b3708e41a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="Rac93220ca00a4a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="R8e3e9088ea7c4dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="Rf2be7eaf67b14ebb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="Ra13bbf7e98844260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="Ra481e153e37946bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="Rc1cb36b4258042ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6b834443fdee4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R364d17161ab34ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messages" sheetId="3" r:id="Rf2447209fd124dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeekDays" sheetId="4" r:id="R32e579714cf84277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserStates" sheetId="5" r:id="Rd160f78336e94bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserSessions" sheetId="6" r:id="Rf900dc25559d4add"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="7" r:id="R6edf2f4829dc4da5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerProfiles" sheetId="8" r:id="R68fc5527bf504f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerVisitHistory" sheetId="9" r:id="R61267945c74d4d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerConflicts" sheetId="10" r:id="R0f6c81f1b1ac4c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomerServiceSettings" sheetId="11" r:id="Rbcb856fbe2264146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="12" r:id="Rf668867768d340ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Providers" sheetId="13" r:id="Ra8ca0b7c89354294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderSchedule" sheetId="14" r:id="R1e2001fdb4f345ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProviderScheduleOverrides" sheetId="15" r:id="Re1e0d61d53a84ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" r:id="R17bdb9ed2ac8432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="17" r:id="Rae655bc071f14ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestOptions" sheetId="18" r:id="Rdc26faed55184c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequestRecipients" sheetId="19" r:id="R88e5d5d56ee94c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appointments" sheetId="20" r:id="R557a066ab9724fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="21" r:id="Rf717e1fdfc8a473a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31608,20 +31608,20 @@
         <x:v>recipient_001</x:v>
       </x:c>
       <x:c r="B2" s="50" t="str">
-        <x:v>Первый администратор</x:v>
+        <x:v>Доп. получатель</x:v>
       </x:c>
       <x:c r="C2" s="49" t="str">
-        <x:v>PASTE_FIRST_ADMIN_TELEGRAM_ID</x:v>
+        <x:v>PASTE_TELEGRAM_ID</x:v>
       </x:c>
       <x:c r="D2" s="49" t="str"/>
       <x:c r="E2" s="50" t="str">
-        <x:v>ADMIN</x:v>
+        <x:v>OPTIONAL</x:v>
       </x:c>
       <x:c r="F2" s="51" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="51" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
